--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OKLAHOMA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OKLAHOMA_2013.xlsx
@@ -2227,7 +2227,7 @@
         <v>96</v>
       </c>
       <c r="D104">
-        <v>0.009057458250778</v>
+        <v>0.009057458250778002</v>
       </c>
     </row>
     <row r="105">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C113">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C167">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C262">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C583">
@@ -10993,7 +10993,7 @@
         <v>96</v>
       </c>
       <c r="D591">
-        <v>0.009057458250778</v>
+        <v>0.009057458250778002</v>
       </c>
     </row>
     <row r="592">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C648">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C953">
